--- a/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+          <t>h_01KX55KZG2PA5N986S4ZG7KW6R</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55KZG2PA5N986S4ZG7KW6R</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,41 +605,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Advanced settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KX55KZG2PA5N986S4ZG7KW6R</t>
+          <t>h_01KX564VSGVD3M22459CP8GRN0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55KZG2PA5N986S4ZG7KW6R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX564VSGVD3M22459CP8GRN0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
+          <t>h_01KX570EBHN5EQAB9BJXPEXZ43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55QJZAW6R5CD1WMG5T6PZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX570EBHN5EQAB9BJXPEXZ43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advanced settings</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,195 +671,195 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KX564VSGVD3M22459CP8GRN0</t>
+          <t>h_01KX57569JSJCSDPEW0QFN1RQ8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX564VSGVD3M22459CP8GRN0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX57569JSJCSDPEW0QFN1RQ8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Filter Employees</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KX570EBHN5EQAB9BJXPEXZ43</t>
+          <t>h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX570EBHN5EQAB9BJXPEXZ43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Employee Filter Configuration</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KX57569JSJCSDPEW0QFN1RQ8</t>
+          <t>h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX57569JSJCSDPEW0QFN1RQ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
+          <t>h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
+          <t>h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
+          <t>h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
+          <t>h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,41 +891,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
+          <t>h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,78 +935,78 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KX5MB2VHM325D81JCJHCSGGW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MB2VHM325D81JCJHCSGGW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
+          <t>h_01KX5MC90TA4MN9KRW6H6BTANT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MC90TA4MN9KRW6H6BTANT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KX5MB2VHM325D81JCJHCSGGW</t>
+          <t>h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MB2VHM325D81JCJHCSGGW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KX5MC90TA4MN9KRW6H6BTANT</t>
+          <t>h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MC90TA4MN9KRW6H6BTANT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
         </is>
       </c>
     </row>
@@ -1018,68 +1018,68 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
+          <t>h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
+          <t>h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KX5PCFYFR5F7TYG73TB4EZSY</t>
+          <t>h_01KX5PCW5N8XZZTWWFERPK259X</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5PCFYFR5F7TYG73TB4EZSY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5PCW5N8XZZTWWFERPK259X</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KX5PCW5N8XZZTWWFERPK259X</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5PCW5N8XZZTWWFERPK259X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,32 +1133,10 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,117 +617,117 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Advanced settings</t>
+          <t>Filter Employees</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KX564VSGVD3M22459CP8GRN0</t>
+          <t>h_01KX570EBHN5EQAB9BJXPEXZ43</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX564VSGVD3M22459CP8GRN0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX570EBHN5EQAB9BJXPEXZ43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Filter Employees</t>
+          <t>Employee Filter Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KX570EBHN5EQAB9BJXPEXZ43</t>
+          <t>h_01KX57569JSJCSDPEW0QFN1RQ8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX570EBHN5EQAB9BJXPEXZ43</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX57569JSJCSDPEW0QFN1RQ8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Employee Filter Configuration</t>
+          <t>Filter Candidates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KX57569JSJCSDPEW0QFN1RQ8</t>
+          <t>h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX57569JSJCSDPEW0QFN1RQ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KXJGJSM42FYWAZBX1WWC2KG5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Service Desk</t>
+          <t>Candidate Filter Configuration</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
+          <t>h_01KYHNQQ78VXVJHAM5B6BTK65N</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KYHNQQ78VXVJHAM5B6BTK65N</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Service Desk</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
+          <t>h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JDJTEZ8M9FJTJEZ8MNYSF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JML Ticket Creation</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,173 +737,173 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
+          <t>h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JFH694QCW2WDV0Z8BMG4R</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ticket Creation Configuration</t>
+          <t>JML Ticket Creation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
+          <t>h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JGQY52CH0QXAJ1EKHS0C6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Ticket Creation Configuration</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
+          <t>h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5JJPAB97DXDJZWRKXZAZW2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
+          <t>h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KQVEKBEZVZ03Q51AX9FG2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Define Notification Channel</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5KV3JGW5JHPVPDG9BVT0GH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification Configuration</t>
+          <t>Define Notification Channel</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KSFFXMC8DGHWE6ESQJQQF281</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Notification Configuration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
+          <t>h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7V6X68TA0NPF6YFYGCPB2N</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Global Operational Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M4Z55MS7BN5Z15Q11RK3Y</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
+          <t>h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KV7W4KZY1XFCJ3YSFXQMJHP9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,85 +935,85 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KX5MB2VHM325D81JCJHCSGGW</t>
+          <t>h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MB2VHM325D81JCJHCSGGW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5M9XVSS0HB3PE09Y73Z9NT</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KX5MC90TA4MN9KRW6H6BTANT</t>
+          <t>h_01KX5MB2VHM325D81JCJHCSGGW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MC90TA4MN9KRW6H6BTANT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MB2VHM325D81JCJHCSGGW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
+          <t>h_01KX5MC90TA4MN9KRW6H6BTANT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MC90TA4MN9KRW6H6BTANT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Operation Safeguard Settings</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
+          <t>h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MEPCQ7BEN4ZQ79MRF1DFC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Advanced Settings</t>
+          <t>Operation Safeguard Settings</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,120 +1023,142 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
+          <t>h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5N7BWRZRJK6V3WP05BMCCN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Advanced Settings</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+          <t>h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5MZWMHR1A64HAXDS02Q4DQ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Service Desk Bridge</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX55H7MQ8J7D8ZSFXEMNG03Q</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Service Desk Bridge</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KX5PCW5N8XZZTWWFERPK259X</t>
+          <t>h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5PCW5N8XZZTWWFERPK259X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KW1TH82EGE4EW275DJSB2X28</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KX5PCW5N8XZZTWWFERPK259X</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01KX5PCW5N8XZZTWWFERPK259X</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-Zendesk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-Zendesk-Integration-Guide/headings.xlsx
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H5</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
